--- a/results/Int Task Remove ACC 0.4/Linea_fi_all.xlsx
+++ b/results/Int Task Remove ACC 0.4/Linea_fi_all.xlsx
@@ -1016,7 +1016,7 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>-0.06732804232804236 +/- 0.005313188359480179</t>
+          <t>-0.06737213403880074 +/- 0.005282915626366904</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>-0.024647266313933026 +/- 0.0012384984043375805</t>
+          <t>-0.024603174603174637 +/- 0.0012123216124221763</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.06798561151079141 +/- 0.0034054129907844523</t>
+          <t>0.06803057553956839 +/- 0.0034423187132056193</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>-0.00022482014388486293 +/- 0.00150813937331372</t>
+          <t>-0.00026978417266183553 +/- 0.0014104664695466199</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.017592160522631815 +/- 0.0023980709580083233</t>
+          <t>0.017638824078394767 +/- 0.0024585982029527737</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>-0.0003733084461035929 +/- 0.0011392025772966588</t>
+          <t>-0.00032664489034064383 +/- 0.0011997162979171662</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0.2478743068391867 +/- 0.008089384348293508</t>
+          <t>0.24782809611829953 +/- 0.00809690426556572</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>0.02100563909774439 +/- 0.00246027069787752</t>
+          <t>0.02105263157894739 +/- 0.002449025229472815</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -3381,7 +3381,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>0.0037462750106428524 +/- 0.0033779198680080505</t>
+          <t>0.003703703703703731 +/- 0.0033738935804298793</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
@@ -3561,7 +3561,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.028958691910499147 +/- 0.0069783059597694295</t>
+          <t>0.028915662650602424 +/- 0.006996192456696258</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.003184165232358016 +/- 0.004342332465247113</t>
+          <t>0.0031411359724612953 +/- 0.004362963259969454</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.0003012048192771122 +/- 0.004586402401848812</t>
+          <t>0.0003442340791738441 +/- 0.004641578850313885</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-0.04661164205039096 +/- 0.0028818433172236404</t>
+          <t>-0.04669852302345786 +/- 0.002843610399487956</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -4026,72 +4026,72 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>0.0024326672458731768 +/- 0.0006204542509593919</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>-0.02206776715899217 +/- 0.0030888599191365965</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0.005343179843614254 +/- 0.005165766146602647</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>0.005343179843614254 +/- 0.005165766146602647</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>0.006993918331885329 +/- 0.0021143516114053677</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>-0.04752389226759337 +/- 0.0037277911299608986</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>-0.03483927019982621 +/- 0.0034687167293965425</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0.0008688097306690068 +/- 0.004597308967966257</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0.008470894874022616 +/- 0.002459284075537496</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>-0.03970460469157253 +/- 0.0042349461709657475</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>0.15013032145960037 +/- 0.0054886500337401</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>-0.0004778453518679227 +/- 0.0009407648926024244</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>0.23996524761077326 +/- 0.004443687872300406</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
           <t>0.002345786272806272 +/- 0.0007058243618276114</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>-0.02206776715899217 +/- 0.0030888599191365965</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>0.005343179843614254 +/- 0.005165766146602647</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>0.005343179843614254 +/- 0.005165766146602647</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>0.006993918331885329 +/- 0.0021143516114053677</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>-0.04752389226759337 +/- 0.0037277911299608986</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>-0.03483927019982621 +/- 0.0034687167293965425</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0.0008688097306690068 +/- 0.004597308967966257</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0.008470894874022616 +/- 0.002459284075537496</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>-0.03970460469157253 +/- 0.0042349461709657475</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>0.15013032145960037 +/- 0.0054886500337401</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>-0.0004778453518679227 +/- 0.0009407648926024244</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>0.23996524761077326 +/- 0.004443687872300406</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>0.0023892267593397243 +/- 0.0007333598182508193</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -4916,74 +4916,74 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>0.0020189003436426045 +/- 0.0009222899722329816</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>0.0230240549828179 +/- 0.004222751109087444</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0.0036512027491408805 +/- 0.003961450038386429</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>0.0036512027491408805 +/- 0.003961450038386429</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>-0.0028780068728522235 +/- 0.003415151067062008</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0.18182989690721651 +/- 0.005082724285129211</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>-0.0014604810996563522 +/- 0.0030325365283028743</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>0.007001718213058406 +/- 0.0030859149580175047</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>-0.00021477663230240474 +/- 0.0021499130165364526</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>0.023195876288659822 +/- 0.0032600800620292457</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>0.5006013745704468 +/- 0.006503725814876313</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>-0.003307560137457033 +/- 0.0022241569529208886</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>0.17830756013745705 +/- 0.006458887214731433</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
           <t>0.0019759450171821236 +/- 0.000964344687312868</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>0.0230240549828179 +/- 0.004222751109087444</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0.0036512027491408805 +/- 0.003961450038386429</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>0.0036512027491408805 +/- 0.003961450038386429</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>-0.0028780068728522235 +/- 0.003415151067062008</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>0.181872852233677 +/- 0.005006461266093956</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>-0.0014604810996563522 +/- 0.0030325365283028743</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>0.007001718213058406 +/- 0.0030859149580175047</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>-0.00021477663230240474 +/- 0.0021499130165364526</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>0.023195876288659822 +/- 0.0032600800620292457</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>0.5006013745704468 +/- 0.006503725814876313</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>-0.003307560137457033 +/- 0.0022241569529208886</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>0.17830756013745705 +/- 0.006458887214731433</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>0.0019759450171821236 +/- 0.000964344687312868</t>
-        </is>
-      </c>
       <c r="W11" t="inlineStr">
         <is>
           <t>0.015292096219931295 +/- 0.0035432286301205263</t>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>0.004123711340206171 +/- 0.002007443547344997</t>
+          <t>0.00408075601374569 +/- 0.001998692461191031</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
